--- a/2-Working-With-Data/06-non-relational/CocaColaCo.xlsx
+++ b/2-Working-With-Data/06-non-relational/CocaColaCo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10315"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jasmineg\projects\Data-Science-For-Beginners\2-Working-With-Data\06-non-relational\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junkang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{291207B9-196B-4B03-8D34-EB4EEEE77362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC44392-219D-E446-ACD3-D9A92EA0513B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="500" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COCA COLA CO" sheetId="1" r:id="rId1"/>
@@ -89,21 +89,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="176" formatCode="\$#,##0.00"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -121,6 +111,25 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="나눔명조"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="3">
@@ -159,16 +168,16 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="3" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="통화" xfId="1" builtinId="4"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -470,21 +479,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="134.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="12" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="134.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="12" width="11.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -519,114 +528,133 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="1:12">
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>30990</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4" s="4">
         <v>35119</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="4">
         <v>46542</v>
       </c>
-      <c r="F4" s="5">
+      <c r="F4" s="4">
         <v>48017</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="4">
         <v>46854</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4" s="4">
         <v>45998</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="4">
         <v>44294</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4" s="4">
         <v>41863</v>
       </c>
-      <c r="K4" s="5">
+      <c r="K4" s="4">
         <v>35410</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="4">
         <v>31856</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12">
       <c r="B5" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="4">
         <v>11088</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>12693</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="4">
         <v>18215</v>
       </c>
-      <c r="F5" s="5">
+      <c r="F5" s="4">
         <v>19053</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="4">
         <v>18421</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5" s="4">
         <v>17889</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="4">
         <v>17482</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5" s="4">
         <v>16465</v>
       </c>
-      <c r="K5" s="5">
+      <c r="K5" s="4">
         <v>13255</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="4">
         <v>11770</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12">
       <c r="B6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="5">
         <v>19902</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="5">
         <v>22426</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="5">
         <v>28327</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="5">
         <v>28964</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="5">
         <v>28433</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="5">
         <f>H4-H5</f>
         <v>28109</v>
       </c>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
+      <c r="I6" s="6">
+        <f>I4-I5</f>
+        <v>26812</v>
+      </c>
+      <c r="J6" s="6">
+        <f>J4-J5</f>
+        <v>25398</v>
+      </c>
+      <c r="K6" s="6">
+        <f>K4-K5</f>
+        <v>22155</v>
+      </c>
+      <c r="L6" s="6">
+        <f>L4-L5</f>
+        <v>20086</v>
+      </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="3" t="s">
+    <row r="8" spans="1:12">
+      <c r="B8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="C9" s="7">
+        <f>AVERAGE(C6:L6)</f>
+        <v>25061.200000000001</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/2-Working-With-Data/06-non-relational/CocaColaCo.xlsx
+++ b/2-Working-With-Data/06-non-relational/CocaColaCo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junkang/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BC44392-219D-E446-ACD3-D9A92EA0513B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DE0BC81-ABA5-D146-8292-3D6676435BE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -165,7 +165,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -174,6 +174,7 @@
     <xf numFmtId="44" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="176" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="통화" xfId="1" builtinId="4"/>
@@ -479,7 +480,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
@@ -652,6 +653,9 @@
         <v>25061.200000000001</v>
       </c>
     </row>
+    <row r="12" spans="1:12">
+      <c r="C12" s="8"/>
+    </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <phoneticPr fontId="5" type="noConversion"/>
